--- a/Sync/Documents/FujiSync4D.Issues_03292012.xlsx
+++ b/Sync/Documents/FujiSync4D.Issues_03292012.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="30" windowWidth="15195" windowHeight="11760" activeTab="1"/>
+    <workbookView xWindow="120" yWindow="30" windowWidth="15195" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="03292012" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="45">
   <si>
     <t>Sr.No</t>
   </si>
@@ -483,18 +483,9 @@
     <t>Please change footer of website as shown in mockup website</t>
   </si>
   <si>
-    <t>InProgress</t>
-  </si>
-  <si>
     <t>Done</t>
   </si>
   <si>
-    <t>Question To Ask</t>
-  </si>
-  <si>
-    <t>Partially Done</t>
-  </si>
-  <si>
     <t>Related to TaskNo. 7</t>
   </si>
   <si>
@@ -1135,6 +1126,9 @@
   </si>
   <si>
     <t>General</t>
+  </si>
+  <si>
+    <t>In Progress</t>
   </si>
 </sst>
 </file>
@@ -1570,16 +1564,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -1590,10 +1584,10 @@
         <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -1604,10 +1598,10 @@
         <v>4</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -1618,10 +1612,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -1629,19 +1623,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -1652,10 +1646,10 @@
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -1666,10 +1660,10 @@
         <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="135" x14ac:dyDescent="0.25">
@@ -1680,10 +1674,10 @@
         <v>8</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -1694,7 +1688,7 @@
         <v>9</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
         <v>15</v>
@@ -1708,13 +1702,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" t="s">
         <v>44</v>
       </c>
-      <c r="D10" t="s">
-        <v>18</v>
-      </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="75" x14ac:dyDescent="0.25">
@@ -1725,13 +1719,13 @@
         <v>11</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" t="s">
         <v>44</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>21</v>
-      </c>
-      <c r="E11" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -1739,19 +1733,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -1762,10 +1756,10 @@
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="60" x14ac:dyDescent="0.25">
@@ -1776,10 +1770,10 @@
         <v>13</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1790,10 +1784,10 @@
         <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1809,6 +1803,7 @@
   <cols>
     <col min="2" max="2" width="104.140625" customWidth="1"/>
     <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1819,16 +1814,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -1836,10 +1831,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -1847,10 +1842,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1858,10 +1853,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -1869,10 +1864,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="60" x14ac:dyDescent="0.25">
@@ -1880,10 +1875,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="62.25" x14ac:dyDescent="0.25">
@@ -1891,10 +1886,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1902,10 +1897,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -1913,10 +1908,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1924,10 +1922,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -1935,10 +1933,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1946,10 +1944,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="60" x14ac:dyDescent="0.25">
@@ -1957,10 +1955,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1968,10 +1966,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>42</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/Sync/Documents/FujiSync4D.Issues_03292012.xlsx
+++ b/Sync/Documents/FujiSync4D.Issues_03292012.xlsx
@@ -4,19 +4,19 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="30" windowWidth="15195" windowHeight="11760"/>
+    <workbookView xWindow="120" yWindow="30" windowWidth="15195" windowHeight="11760" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="03292012" sheetId="1" r:id="rId1"/>
     <sheet name="03302012" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="04032012" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="67">
   <si>
     <t>Sr.No</t>
   </si>
@@ -1129,13 +1129,1095 @@
   </si>
   <si>
     <t>In Progress</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On DeviceList Page </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Please put button for "Clear Filter".</t>
+    </r>
+  </si>
+  <si>
+    <t>DeviceList</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">On Devicelist Page </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Right now there is no User Management. Everyone can see everything under same region. Please display list of company, branch and devices according to user level. (e.g., if user is Company Admin, he can only see his company name in company selection box, all branches under that company and all devices under that company. Same rule applies to Branch Admin, he can only able to see his company, his branch and devices under his branch only. So please customize all options accordingly logged on user’s role level.)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">On Project List/ DLP Optimization List Page </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Please provide sorting option for list.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On Project List/ DLP Optimization List Page </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Please put “Clear Filter” button instead of this image at top right side to make looks consistent compared to Admin section’s list pages.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On Project List/ DLP Optimization List </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if I click on “Create New Print Condition” on top </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">under step1. Description </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Please change requiredfieldvalidator’s error message for “Rip settings” from “Please provide colorant name” instead of “Please provide rip settings”.  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On Project List/ DLP Optimization List </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if I click on “Create New Print Condition” on top </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">under step5. Save </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if I click on “Confirm Save” button </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> I opens popup window, where if I click on “DawnLoad Chart” button </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> it doesn’t let me download anything. + please change spelling of this button too.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On Project List/ DLP Optimization List </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if I click on “Create New Print Condition” on top </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">under step5. Save </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if I click on “Confirm Save” button </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> I opens popup window, next right to “DawnLoad Chart” button, please give the correct name of chart (right now it shows "sync 500" for every chart type).</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">On Project List Page </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> When I click on one project (open status) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> it display message in pop up window as: “Current Run -1 is open and has been inactive for 0 days. Confirm which DLP is used in your workflow. The current DLP is “Dhruti_Fuji500 DLP -2 ". --&gt; (Notes: in this project I just went till step 5. Save under create new print condition. There is no measurement added, so no DLP created under this project, then how come it shows this kind of message in pop up window.)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On Project List/ DLP Optimization List </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if I click on “Create New Print Condition” on top </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">under step6. Measure </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if I click on “Analyze” button </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> it display alert message as shown in below image then opens analyze page. So please remove this alert message.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">On Project List/ DLP Optimization List --&gt; if I click on “Create New Print Condition” on top --&gt; under step7. Analyze --&gt; Let's say I have 2 measurement uploaded, so here on top "Analyze Measurement:sheet_01" chart, it shows me 2 checkboxes. If I uncheck any of the the checkbox of X-axis, it hides chart and shows me an error. </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On Project List/ DLP Optimization List </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if I click on “Create New Print Condition” on top </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">under step7. Analyze </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if I click on “Download DLP” button </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">it display popup window for “Creating DLP, please wait…. Once optimization is complete, apply DLP 000 to workflow and repaint the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Sync 500 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">patch chart.”  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Please change “Sync 500” to original chart name.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">For All GridView/ListView on all pages throughout website </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Please give sorting option enabled.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On Branch Management List </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Cannot able to filter for “CompanyName” column.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On User Management List </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> on Add User </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> I am getting “JRhayes” by default in the User Name textbox. Please make it blank.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On User Management List </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> On Add/Edit User </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if I select “Fujifilm North America – Graphic Systems” as a company name, it automatically display “North America” as a region, but when I hit “Save” button </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> it is storing “RegionID=NULL” in DB in “CP.User” table. (Please make sure if I select company, it automatically getting RegionID for that company, so it can't be NULL for those users. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Notes:- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>If I am logged on user whose Role is below "Region Admin", I will only able to see my relavent options for company, branch selection for this newly creating user according to my Role Level. e.g., if I am a company Admin, I have only option to create users under my company. If I am a Branch Admin, I can only create users under my branch only.)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Under Admin section </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> On Add User Page </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> I choose one company (e.g., HC Johnson) and 2 branches under that for this user and give Role as “License Admin” </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> after saving new user successfully when I go to login page with this user’s credentials. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> it throws me an error as below:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On User Management List </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Cannot able to filter for “Branch” column.</t>
+    </r>
+  </si>
+  <si>
+    <t>On User Management List, there is not any proper user management applied means let's see if I am login as a "company admin" or "Branch Admin", I can only able to see users under my branch or under my branch respectively. Right now it shows me everyone under that company and those users who is not related to any company too.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On SourceProfileList </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Give option to download source profile (.icc file) when we click on “Click Me!” link from the list.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">On SourceProfileList </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Add/Edit SourceProfile </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Let user select first “Region” then according to that, below selection box of “company” displays the records. + Please give requiredfieldvalidator for “Region”, because it can’t be NULL. User can leave company as NULL, then this sourceprofile is works as a global profile under all companies of this selected region.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On Measurement Device Management List </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Add Measurement Device </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Please put error messages for requiredfieldvalidators. Right now, if I don’t fill anything, and click on “Save” button </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> it doesn’t do anything + doesn’t display any error messages that way user will know what is wrong.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1205,6 +2287,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1226,7 +2314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1245,6 +2333,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1980,9 +3083,265 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="53.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="150" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="135" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="210" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Sync/Documents/FujiSync4D.Issues_03292012.xlsx
+++ b/Sync/Documents/FujiSync4D.Issues_03292012.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="69">
   <si>
     <t>Sr.No</t>
   </si>
@@ -2211,6 +2211,12 @@
       </rPr>
       <t xml:space="preserve"> it doesn’t do anything + doesn’t display any error messages that way user will know what is wrong.</t>
     </r>
+  </si>
+  <si>
+    <t>Partially Done</t>
+  </si>
+  <si>
+    <t>Rules of password strength remaining</t>
   </si>
 </sst>
 </file>
@@ -2961,6 +2967,9 @@
       <c r="C4" s="6" t="s">
         <v>43</v>
       </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
@@ -2972,6 +2981,9 @@
       <c r="C5" s="6" t="s">
         <v>41</v>
       </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="6" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
@@ -2994,6 +3006,9 @@
       <c r="C7" s="6" t="s">
         <v>41</v>
       </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
@@ -3017,7 +3032,7 @@
         <v>42</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -3030,6 +3045,9 @@
       <c r="C10" s="7" t="s">
         <v>42</v>
       </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
@@ -3041,6 +3059,9 @@
       <c r="C11" s="7" t="s">
         <v>42</v>
       </c>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
@@ -3052,6 +3073,9 @@
       <c r="C12" s="7" t="s">
         <v>42</v>
       </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="13" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
@@ -3063,6 +3087,12 @@
       <c r="C13" s="7" t="s">
         <v>42</v>
       </c>
+      <c r="D13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
@@ -3073,6 +3103,9 @@
       </c>
       <c r="C14" s="7" t="s">
         <v>42</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -3120,6 +3153,9 @@
       <c r="C2" s="11" t="s">
         <v>46</v>
       </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="3" spans="1:6" ht="150" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -3142,6 +3178,9 @@
       <c r="C4" s="8" t="s">
         <v>41</v>
       </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="5" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A5">
@@ -3153,6 +3192,9 @@
       <c r="C5" s="8" t="s">
         <v>41</v>
       </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="6" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -3164,6 +3206,9 @@
       <c r="C6" s="8" t="s">
         <v>41</v>
       </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A7">
@@ -3208,6 +3253,9 @@
       <c r="C10" s="8" t="s">
         <v>41</v>
       </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A11">
@@ -3275,7 +3323,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3286,7 +3334,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3296,8 +3344,11 @@
       <c r="C18" s="13" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="105" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3308,7 +3359,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3319,7 +3370,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="105" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3330,7 +3381,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>

--- a/Sync/Documents/FujiSync4D.Issues_03292012.xlsx
+++ b/Sync/Documents/FujiSync4D.Issues_03292012.xlsx
@@ -4,19 +4,20 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="30" windowWidth="15195" windowHeight="11760" activeTab="2"/>
+    <workbookView xWindow="120" yWindow="30" windowWidth="15195" windowHeight="11760" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="03292012" sheetId="1" r:id="rId1"/>
     <sheet name="03302012" sheetId="2" r:id="rId2"/>
     <sheet name="04032012" sheetId="3" r:id="rId3"/>
+    <sheet name="04042012" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="76">
   <si>
     <t>Sr.No</t>
   </si>
@@ -2217,6 +2218,426 @@
   </si>
   <si>
     <t>Rules of password strength remaining</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On DeviceList Page </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> If I choose "Fujifilm North America-Graphic Systems" as a company and "Hanover Park" as branch --&gt; below devicelist is updated accordigly. --&gt; When I hit some filtering in "DeviceName" column on list --&gt; it will filterout from all devices and display them inspite of they belongs to some other company or some other branch. Means during filter they are not checking whether we selected some company and/or branch above or not.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On Project List/ DLP Optimization List </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if I click on existing open project and press "continue" button from popup </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">under Analyze </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if I click on “Save” button --&gt; it shows 2 options in popup , and lets say I choose "No,Optimize" button </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">it display popup window for “Creating DLP, please wait…. Once optimization is complete, apply </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DLP 000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to workflow and repaint the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Sync 500 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">patch chart.”  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Please change “Sync 500” to original chart name and "DLP 000" to "DLP 001 0r 002" whatever the current run's number is.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On Project List/ DLP Optimization List </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if I click on any existing project and press "continue" button from popup(if project is open) or press "Re-Optimize" button from popup(if project is closed) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">under Measure </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Please change top page title "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Measure - Test By Jay 1.icc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" to "Measure - Test By Jay 1 DLP 002.icc" (let's assume we are in run 3's Measure page right now)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On Project List/ DLP Optimization List </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if I click on any existing project and press "continue" button from popup(if project is open) or press "Re-Optimize" button from popup(if project is closed) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">under Analyze </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Please change top page title "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Analyze - Test By Jay 1.icc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" to "Analyze - Test By Jay 1 DLP 002.icc" (let's assume we are in run 3's Analyze page right now)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">On Admin </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">under Measurement Device List </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for Add/Update </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> please put some regularexpressionvalidator for "Serial Number" textbox that way, it only accepts numerical values [0-9].</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Please change </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>project status to only 2 options: Open and Closed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, No certify. --&gt; When for any project user select "No,Certify" on analyze page, that run will saved as "closed" in database and it contains same popup window as with 3 buttons options (re-optimize, view last analysis, download current DLP). All other project stages consider as a "open" status, like if user click on "No,Optimize" button or he goes to Analyze page and don't click on "Save" button or may be user create DLP for current run after selecting "No,Optimize" button and forget to make/create another measurement for that project, all these conditions marked as a "open" project. </t>
+    </r>
+  </si>
+  <si>
+    <t>On Admin --&gt; under User Management List --&gt; for Add/Edit User --&gt; Please put "Role" selectionlist as below roles only.
+Role: Company Admin,Branch Admin, Site User
+If logged on user's role is above Company Admin, then he can see above list and if user's role is &lt;= Company Admin, he can only able to see its below level roles. (Let's say if I am Company Admin --&gt; I can only able to create users as Branch Admin and Site Users; if I am Branch Admin --&gt; I can only able to create Site Users.)</t>
   </si>
 </sst>
 </file>
@@ -2320,7 +2741,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2354,6 +2775,45 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3395,4 +3855,121 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="73.42578125" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="11">
+        <v>1</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+      <c r="A3" s="17">
+        <v>2</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="A4" s="18">
+        <v>3</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="A5" s="18">
+        <v>4</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="18">
+        <v>5</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A7" s="22">
+        <v>6</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+      <c r="A8" s="24">
+        <v>7</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="26"/>
+      <c r="C9" s="25"/>
+    </row>
+    <row r="10" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Sync/Documents/FujiSync4D.Issues_03292012.xlsx
+++ b/Sync/Documents/FujiSync4D.Issues_03292012.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="30" windowWidth="15195" windowHeight="11760" activeTab="3"/>
+    <workbookView xWindow="120" yWindow="30" windowWidth="15195" windowHeight="11760" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="03292012" sheetId="1" r:id="rId1"/>
@@ -3308,7 +3308,7 @@
         <v>41</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>19</v>

--- a/Sync/Documents/FujiSync4D.Issues_03292012.xlsx
+++ b/Sync/Documents/FujiSync4D.Issues_03292012.xlsx
@@ -4,20 +4,21 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="30" windowWidth="15195" windowHeight="11760" activeTab="2"/>
+    <workbookView xWindow="120" yWindow="30" windowWidth="15195" windowHeight="11760" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="03292012" sheetId="1" r:id="rId1"/>
     <sheet name="03302012" sheetId="2" r:id="rId2"/>
     <sheet name="04032012" sheetId="3" r:id="rId3"/>
     <sheet name="04042012" sheetId="4" r:id="rId4"/>
+    <sheet name="04052012" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="82">
   <si>
     <t>Sr.No</t>
   </si>
@@ -499,15 +500,9 @@
     <t>It's very fast,so it might not need to put wait control. Will check it.</t>
   </si>
   <si>
-    <t>I have already sent an email regarding this.How program should behave if user clicks on certify project.</t>
-  </si>
-  <si>
     <t>we haven't think about editing project. We have completely missed this part.</t>
   </si>
   <si>
-    <t>For now, just make behavior of certify project same as closed project. 3 options: re-optimize, download current DLP and close as same as we did in mock up website.</t>
-  </si>
-  <si>
     <t>Dhruti's Notes</t>
   </si>
   <si>
@@ -1127,9 +1122,6 @@
   </si>
   <si>
     <t>General</t>
-  </si>
-  <si>
-    <t>In Progress</t>
   </si>
   <si>
     <r>
@@ -2638,6 +2630,34 @@
     <t>On Admin --&gt; under User Management List --&gt; for Add/Edit User --&gt; Please put "Role" selectionlist as below roles only.
 Role: Company Admin,Branch Admin, Site User
 If logged on user's role is above Company Admin, then he can see above list and if user's role is &lt;= Company Admin, he can only able to see its below level roles. (Let's say if I am Company Admin --&gt; I can only able to create users as Branch Admin and Site Users; if I am Branch Admin --&gt; I can only able to create Site Users.)</t>
+  </si>
+  <si>
+    <t>On DeviceList Page --&gt; there is some issue with AJAX --&gt; on Windows 7 machine, I have to click on any press (device name) for 2-3 times then it is open and redirect me to operation selection page. On Mac machine, I have to click on devicename like 8-9 times then finally I will able to redirect on another page (I feel like there is some problem with AJAX, after clicking devicename it shows ajax-loading image but doesn't do anything).</t>
+  </si>
+  <si>
+    <t>On ProjectList --&gt; Select "Create new Print Condition" --&gt; On "step 4. Measurement Setup" --&gt; select "10°" for "observer" --&gt; after creating project --&gt; go to measurement page --&gt; click on "measure chart" button --&gt; it shows error as below:</t>
+  </si>
+  <si>
+    <t>On ProjectList --&gt; Select "Create new Print Condition" --&gt; after creating project  and making DLP --&gt; make run-1's DLP too--&gt; go to download page of run 1--&gt; back on "project list" page again --&gt; click on that newly added project, it's state is "open" --&gt; on popup window, it shows wrong message "Current Run 2 is open and has been inactive for 0 days.
+Confirm which DLP is used in your workflow. The current DLP is " Dhruti_Test_1650Visual DLP 1 " . --&gt; we didn't make run 2 yet, we just finish run 1 --&gt; when we click on "Continue" button --&gt; it redirect us to "Analyze" page of run 1, then why you mention current run is 2 on pop up message. --&gt; Please make corrections.</t>
+  </si>
+  <si>
+    <t>Admin --&gt; Branch List Page --&gt; if you try to delete any branch from list --&gt; it hides whole listview control and page become blank + that branch is also not deleted.</t>
+  </si>
+  <si>
+    <t>As we are not concern about Certify project, this issue resolves itself.</t>
+  </si>
+  <si>
+    <t>For some chart, database doesn't have images.We need to add that to database field.</t>
+  </si>
+  <si>
+    <t>I guess this is related to browser cache. Browser saves username and password from any site and show it in this box. Although we will look into this.</t>
+  </si>
+  <si>
+    <t>I guess we need to talk on this. I am confused: do we need to show a word "certify" anywhere in the UI?</t>
+  </si>
+  <si>
+    <t>mention in email, how to resolve this from database.i have resolve same error with "TwoDegree"</t>
   </si>
 </sst>
 </file>
@@ -2741,7 +2761,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2814,6 +2834,22 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3133,7 +3169,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -3142,7 +3178,7 @@
         <v>17</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -3153,7 +3189,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
@@ -3167,7 +3203,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
         <v>15</v>
@@ -3181,30 +3217,27 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+      <c r="A5" s="30">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="B5" s="30" t="s">
         <v>22</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -3215,7 +3248,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
@@ -3229,7 +3262,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
@@ -3243,7 +3276,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
         <v>15</v>
@@ -3257,7 +3290,7 @@
         <v>9</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
         <v>15</v>
@@ -3271,10 +3304,10 @@
         <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="E10" t="s">
         <v>16</v>
@@ -3288,13 +3321,13 @@
         <v>11</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3302,10 +3335,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>15</v>
@@ -3314,7 +3347,7 @@
         <v>19</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -3325,7 +3358,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
@@ -3339,7 +3372,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s">
         <v>15</v>
@@ -3353,7 +3386,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
@@ -3383,7 +3416,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -3392,7 +3425,7 @@
         <v>17</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -3400,10 +3433,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -3411,10 +3444,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3422,10 +3458,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
@@ -3436,10 +3472,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
@@ -3450,10 +3486,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="62.25" x14ac:dyDescent="0.25">
@@ -3461,10 +3500,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
@@ -3475,10 +3514,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -3486,10 +3525,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>15</v>
@@ -3500,10 +3539,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
         <v>15</v>
@@ -3514,10 +3553,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
         <v>15</v>
@@ -3528,10 +3567,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
         <v>15</v>
@@ -3542,16 +3581,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -3559,10 +3598,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
         <v>15</v>
@@ -3591,7 +3630,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -3600,7 +3639,7 @@
         <v>17</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -3608,10 +3647,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
@@ -3622,10 +3661,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -3633,10 +3672,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
@@ -3647,10 +3686,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
@@ -3661,10 +3700,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
@@ -3675,10 +3714,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="90" x14ac:dyDescent="0.25">
@@ -3686,10 +3731,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="135" x14ac:dyDescent="0.25">
@@ -3697,10 +3745,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="75" x14ac:dyDescent="0.25">
@@ -3708,10 +3756,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
         <v>15</v>
@@ -3722,10 +3770,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="105" x14ac:dyDescent="0.25">
@@ -3733,10 +3784,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -3744,10 +3798,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -3755,10 +3812,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -3766,10 +3826,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="210" x14ac:dyDescent="0.25">
@@ -3777,10 +3843,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="90" x14ac:dyDescent="0.25">
@@ -3788,10 +3857,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -3799,10 +3868,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D18" t="s">
         <v>15</v>
@@ -3813,10 +3882,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="45" x14ac:dyDescent="0.25">
@@ -3824,10 +3893,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="D20" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="105" x14ac:dyDescent="0.25">
@@ -3835,10 +3907,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="90" x14ac:dyDescent="0.25">
@@ -3846,10 +3918,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -3875,7 +3947,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -3889,10 +3961,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>46</v>
+        <v>43</v>
+      </c>
+      <c r="D2" s="29" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="105" x14ac:dyDescent="0.25">
@@ -3900,10 +3975,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="75" x14ac:dyDescent="0.25">
@@ -3911,10 +3989,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="75" x14ac:dyDescent="0.25">
@@ -3922,10 +4003,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="45" x14ac:dyDescent="0.25">
@@ -3933,10 +4017,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="135" x14ac:dyDescent="0.25">
@@ -3944,10 +4031,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="120" x14ac:dyDescent="0.25">
@@ -3955,10 +4048,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -3968,6 +4064,99 @@
     <row r="10" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="25"/>
       <c r="C10" s="25"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="73.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="28">
+        <v>1</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="28">
+        <v>2</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A4" s="28">
+        <v>3</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="32">
+        <v>4</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
